--- a/Taxonomy_list_fermented_food_periodic_table.xlsx
+++ b/Taxonomy_list_fermented_food_periodic_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinzhao/DS_Projects/phylo-tree-fermented-foods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB964AA4-E070-D145-8867-4B5AB75BC9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2E51E4-A2E1-8B4A-BF63-E68A01054B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{D834C665-731C-7E47-A8BF-B2F00BB8B4D6}"/>
+    <workbookView xWindow="4280" yWindow="760" windowWidth="25960" windowHeight="18880" activeTab="3" xr2:uid="{D834C665-731C-7E47-A8BF-B2F00BB8B4D6}"/>
   </bookViews>
   <sheets>
     <sheet name="extracted taxonomy" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="223">
   <si>
     <t xml:space="preserve">Lactobacillaceae  </t>
   </si>
@@ -704,7 +704,13 @@
     <t>Site</t>
   </si>
   <si>
-    <t>Fermented foods</t>
+    <t>Fermented foods1</t>
+  </si>
+  <si>
+    <t>Fermented foods2</t>
+  </si>
+  <si>
+    <t>Species</t>
   </si>
 </sst>
 </file>
@@ -768,7 +774,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -855,11 +861,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -869,52 +886,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1054,6 +1034,42 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
         <name val="Helvetica Neue"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -1308,16 +1324,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7373011F-FAF6-F747-A050-2E8B8CA4E061}" name="Table5" displayName="Table5" ref="C4:J40" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7373011F-FAF6-F747-A050-2E8B8CA4E061}" name="Table5" displayName="Table5" ref="C4:J40" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="C4:J40" xr:uid="{7373011F-FAF6-F747-A050-2E8B8CA4E061}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{8E055767-5C76-A643-9EF9-1957924A029E}" name="Domain" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{846E1FEF-518A-AA4E-9E16-E5059A95343D}" name="Kingdom" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{0A41ECBB-D937-F74D-A994-E7BD4761CF50}" name="Phylum" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{4F76ED4D-1345-9B48-84D3-B3095EA9D28E}" name="Class" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{7202A69A-BC92-F747-BB37-E1374C061A42}" name="Order" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{8307E1DF-BCD3-C845-A288-D669E3EE2CAE}" name="Family" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{92800D17-772F-EA45-84C8-6ECFF9B522C0}" name="Genus" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{8E055767-5C76-A643-9EF9-1957924A029E}" name="Domain" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{846E1FEF-518A-AA4E-9E16-E5059A95343D}" name="Kingdom" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{0A41ECBB-D937-F74D-A994-E7BD4761CF50}" name="Phylum" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{4F76ED4D-1345-9B48-84D3-B3095EA9D28E}" name="Class" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{7202A69A-BC92-F747-BB37-E1374C061A42}" name="Order" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{8307E1DF-BCD3-C845-A288-D669E3EE2CAE}" name="Family" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{92800D17-772F-EA45-84C8-6ECFF9B522C0}" name="Genus" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{8B56D235-2CDB-3942-82E9-3B97E5D8C5E4}" name="Proportion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4003,7 +4019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933E687C-0B8B-8446-9F3B-17B50211A94B}">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
@@ -4232,6 +4248,119 @@
         <v>7</v>
       </c>
       <c r="AK2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>101</v>
+      </c>
+      <c r="K3">
+        <v>101</v>
+      </c>
+      <c r="L3">
+        <v>101</v>
+      </c>
+      <c r="M3">
+        <v>101</v>
+      </c>
+      <c r="N3">
+        <v>101</v>
+      </c>
+      <c r="O3">
+        <v>101</v>
+      </c>
+      <c r="P3">
+        <v>101</v>
+      </c>
+      <c r="Q3">
+        <v>101</v>
+      </c>
+      <c r="R3">
+        <v>101</v>
+      </c>
+      <c r="S3">
+        <v>101</v>
+      </c>
+      <c r="T3">
+        <v>101</v>
+      </c>
+      <c r="U3">
+        <v>101</v>
+      </c>
+      <c r="V3">
+        <v>101</v>
+      </c>
+      <c r="W3">
+        <v>101</v>
+      </c>
+      <c r="X3">
+        <v>101</v>
+      </c>
+      <c r="Y3">
+        <v>101</v>
+      </c>
+      <c r="Z3">
+        <v>101</v>
+      </c>
+      <c r="AA3">
+        <v>101</v>
+      </c>
+      <c r="AB3">
+        <v>101</v>
+      </c>
+      <c r="AC3">
+        <v>101</v>
+      </c>
+      <c r="AD3">
+        <v>101</v>
+      </c>
+      <c r="AE3">
+        <v>101</v>
+      </c>
+      <c r="AF3">
+        <v>101</v>
+      </c>
+      <c r="AG3">
+        <v>9</v>
+      </c>
+      <c r="AH3">
+        <v>9</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>7</v>
+      </c>
+      <c r="AK3">
         <v>7</v>
       </c>
     </row>
@@ -4246,42 +4375,43 @@
   <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" style="11"/>
-    <col min="9" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="H1" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>183</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -4303,8 +4433,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>184</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -4326,8 +4456,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>185</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -4349,8 +4479,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>186</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -4372,8 +4502,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>187</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -4395,8 +4525,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>188</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -4418,8 +4548,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>189</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -4441,8 +4571,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>190</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -4464,8 +4594,8 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>191</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -4487,8 +4617,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>192</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -4510,8 +4640,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>193</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -4533,8 +4663,8 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>194</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -4556,8 +4686,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>195</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -4579,8 +4709,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>196</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -4602,8 +4732,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>197</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -4626,7 +4756,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="A17" t="s">
         <v>198</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -4649,7 +4779,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" t="s">
         <v>199</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -4672,7 +4802,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" t="s">
         <v>200</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -4695,7 +4825,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" t="s">
         <v>201</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -4718,7 +4848,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="A21" t="s">
         <v>202</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -4741,7 +4871,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
+      <c r="A22" t="s">
         <v>203</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -4764,7 +4894,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+      <c r="A23" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="9" t="s">
@@ -4787,7 +4917,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="A24" t="s">
         <v>205</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -4810,7 +4940,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="A25" t="s">
         <v>206</v>
       </c>
       <c r="B25" s="9" t="s">
@@ -4833,7 +4963,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="A26" t="s">
         <v>207</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -4856,7 +4986,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+      <c r="A27" t="s">
         <v>208</v>
       </c>
       <c r="B27" s="9" t="s">
@@ -4879,7 +5009,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+      <c r="A28" t="s">
         <v>209</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -4902,7 +5032,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+      <c r="A29" t="s">
         <v>210</v>
       </c>
       <c r="B29" s="9" t="s">
@@ -4925,7 +5055,7 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+      <c r="A30" t="s">
         <v>211</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -4948,7 +5078,7 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="A31" t="s">
         <v>212</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -4971,7 +5101,7 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+      <c r="A32" t="s">
         <v>213</v>
       </c>
       <c r="B32" s="9" t="s">
@@ -4994,7 +5124,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+      <c r="A33" t="s">
         <v>214</v>
       </c>
       <c r="B33" s="9" t="s">
@@ -5017,7 +5147,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
+      <c r="A34" t="s">
         <v>215</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -5040,7 +5170,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
+      <c r="A35" t="s">
         <v>216</v>
       </c>
       <c r="B35" s="9" t="s">
@@ -5063,7 +5193,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="A36" t="s">
         <v>217</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5086,7 +5216,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
+      <c r="A37" t="s">
         <v>218</v>
       </c>
       <c r="B37" s="10" t="s">

--- a/Taxonomy_list_fermented_food_periodic_table.xlsx
+++ b/Taxonomy_list_fermented_food_periodic_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinzhao/DS_Projects/phylo-tree-fermented-foods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2E51E4-A2E1-8B4A-BF63-E68A01054B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325F09F9-28B9-9247-B071-4FE40D4B5D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="760" windowWidth="25960" windowHeight="18880" activeTab="3" xr2:uid="{D834C665-731C-7E47-A8BF-B2F00BB8B4D6}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{D834C665-731C-7E47-A8BF-B2F00BB8B4D6}"/>
   </bookViews>
   <sheets>
     <sheet name="extracted taxonomy" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="222">
   <si>
     <t xml:space="preserve">Lactobacillaceae  </t>
   </si>
@@ -705,9 +705,6 @@
   </si>
   <si>
     <t>Fermented foods1</t>
-  </si>
-  <si>
-    <t>Fermented foods2</t>
   </si>
   <si>
     <t>Species</t>
@@ -889,7 +886,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4019,7 +4016,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933E687C-0B8B-8446-9F3B-17B50211A94B}">
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
@@ -4248,119 +4245,6 @@
         <v>7</v>
       </c>
       <c r="AK2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>16</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>16</v>
-      </c>
-      <c r="H3">
-        <v>16</v>
-      </c>
-      <c r="I3">
-        <v>16</v>
-      </c>
-      <c r="J3">
-        <v>101</v>
-      </c>
-      <c r="K3">
-        <v>101</v>
-      </c>
-      <c r="L3">
-        <v>101</v>
-      </c>
-      <c r="M3">
-        <v>101</v>
-      </c>
-      <c r="N3">
-        <v>101</v>
-      </c>
-      <c r="O3">
-        <v>101</v>
-      </c>
-      <c r="P3">
-        <v>101</v>
-      </c>
-      <c r="Q3">
-        <v>101</v>
-      </c>
-      <c r="R3">
-        <v>101</v>
-      </c>
-      <c r="S3">
-        <v>101</v>
-      </c>
-      <c r="T3">
-        <v>101</v>
-      </c>
-      <c r="U3">
-        <v>101</v>
-      </c>
-      <c r="V3">
-        <v>101</v>
-      </c>
-      <c r="W3">
-        <v>101</v>
-      </c>
-      <c r="X3">
-        <v>101</v>
-      </c>
-      <c r="Y3">
-        <v>101</v>
-      </c>
-      <c r="Z3">
-        <v>101</v>
-      </c>
-      <c r="AA3">
-        <v>101</v>
-      </c>
-      <c r="AB3">
-        <v>101</v>
-      </c>
-      <c r="AC3">
-        <v>101</v>
-      </c>
-      <c r="AD3">
-        <v>101</v>
-      </c>
-      <c r="AE3">
-        <v>101</v>
-      </c>
-      <c r="AF3">
-        <v>101</v>
-      </c>
-      <c r="AG3">
-        <v>9</v>
-      </c>
-      <c r="AH3">
-        <v>9</v>
-      </c>
-      <c r="AI3">
-        <v>1</v>
-      </c>
-      <c r="AJ3">
-        <v>7</v>
-      </c>
-      <c r="AK3">
         <v>7</v>
       </c>
     </row>
@@ -4407,7 +4291,7 @@
         <v>150</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">

--- a/Taxonomy_list_fermented_food_periodic_table.xlsx
+++ b/Taxonomy_list_fermented_food_periodic_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinzhao/DS_Projects/phylo-tree-fermented-foods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325F09F9-28B9-9247-B071-4FE40D4B5D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78CC614-418B-594F-A8E0-7ACFA388B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{D834C665-731C-7E47-A8BF-B2F00BB8B4D6}"/>
   </bookViews>
@@ -2555,7 +2555,7 @@
   <cols>
     <col min="3" max="3" width="9.1640625" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" customWidth="1"/>
     <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
